--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_GRUPO INMAPA FILIPENSES.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_GRUPO INMAPA FILIPENSES.xlsx
@@ -565,13 +565,13 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>91.6557</v>
+        <v>55.758</v>
       </c>
       <c r="E2" t="n">
-        <v>87.161</v>
+        <v>61.6817</v>
       </c>
       <c r="F2" t="n">
-        <v>4.494199999999999</v>
+        <v>-5.924200000000001</v>
       </c>
       <c r="G2" t="n">
         <v>-24.9723</v>
@@ -610,13 +610,13 @@
         <v>60.7976</v>
       </c>
       <c r="S2" t="n">
-        <v>55.4592</v>
+        <v>19.5618</v>
       </c>
       <c r="T2" t="n">
-        <v>31.5808</v>
+        <v>6.101599999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>23.8787</v>
+        <v>13.4605</v>
       </c>
       <c r="V2" t="n">
         <v>64.2563</v>
@@ -643,13 +643,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1.112</v>
+        <v>1.1656</v>
       </c>
       <c r="E3" t="n">
         <v>0.6443</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4678</v>
+        <v>0.5213</v>
       </c>
       <c r="G3" t="n">
         <v>0.8239</v>
@@ -688,13 +688,13 @@
         <v>0.579</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2908</v>
+        <v>-0.2373</v>
       </c>
       <c r="T3" t="n">
         <v>-0.0595</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2313</v>
+        <v>-0.1778</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. LEON MARTINEZ</t>
+          <t>G. DE LA CRUZ MARTINEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2411</v>
+        <v>0.5061000000000018</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0621</v>
+        <v>3.766699999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.179</v>
+        <v>-3.2606</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1449</v>
+        <v>-0.1385000000000005</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1449</v>
+        <v>-12.7835</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>12.6454</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0621</v>
+        <v>28.6805</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0621</v>
+        <v>10.3637</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>18.3172</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.207</v>
+        <v>-28.8187</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.207</v>
+        <v>-23.1467</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-5.671799999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.386</v>
+        <v>-6.3693</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-35.5133</v>
       </c>
       <c r="R4" t="n">
-        <v>0.386</v>
+        <v>29.144</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-1.2433</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-1.6698</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.4264999999999998</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>8.257099999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>12.2697</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-4.012600000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. SAN JOSE GONZALEZ</t>
+          <t>A. LEON MARTINEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1978</v>
+        <v>0.2411</v>
       </c>
       <c r="E5" t="n">
-        <v>1.44</v>
+        <v>0.0621</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2424</v>
+        <v>0.179</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4302999999999999</v>
+        <v>-0.1449</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8621</v>
+        <v>-0.1449</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2925</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6647</v>
+        <v>0.0621</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5833</v>
+        <v>0.0621</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0814</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.095</v>
+        <v>-0.207</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7212999999999999</v>
+        <v>-0.207</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3739</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.579</v>
+        <v>0.386</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0.386</v>
       </c>
       <c r="S5" t="n">
-        <v>1.821</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7403</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0807</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. RODRIGUEZ HERRON</t>
+          <t>J. SAN JOSE GONZALEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.6672</v>
+        <v>-0.8249</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9991999999999996</v>
+        <v>0.7391</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.6663</v>
+        <v>-1.5639</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8094</v>
+        <v>-0.4302999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>3.26</v>
+        <v>0.8621</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4506000000000001</v>
+        <v>-1.2925</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7029</v>
+        <v>1.6647</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5808</v>
+        <v>1.5833</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1221</v>
+        <v>0.0814</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8935000000000002</v>
+        <v>-2.095</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3207</v>
+        <v>-0.7212999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5727</v>
+        <v>-1.3739</v>
       </c>
       <c r="P6" t="n">
+        <v>-0.579</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-0.965</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-2.123</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.158</v>
+        <v>0.386</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7284</v>
+        <v>0.7985</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2102</v>
+        <v>0.03930000000000003</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9386</v>
+        <v>0.7591</v>
       </c>
       <c r="V6" t="n">
-        <v>-5.24</v>
+        <v>-0.614</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3704</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-4.8696</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. DE LA CRUZ MARTINEZ</t>
+          <t>F. RODRIGUEZ HERRON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.040500000000002</v>
+        <v>-2.8348</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3852</v>
+        <v>1.0994</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.4259</v>
+        <v>-3.9341</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1385000000000005</v>
+        <v>2.8094</v>
       </c>
       <c r="H7" t="n">
-        <v>-12.7835</v>
+        <v>3.26</v>
       </c>
       <c r="I7" t="n">
-        <v>12.6454</v>
+        <v>-0.4506000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>28.6805</v>
+        <v>3.7029</v>
       </c>
       <c r="K7" t="n">
-        <v>10.3637</v>
+        <v>3.5808</v>
       </c>
       <c r="L7" t="n">
-        <v>18.3172</v>
+        <v>0.1221</v>
       </c>
       <c r="M7" t="n">
-        <v>-28.8187</v>
+        <v>-0.8935000000000002</v>
       </c>
       <c r="N7" t="n">
-        <v>-23.1467</v>
+        <v>-0.3207</v>
       </c>
       <c r="O7" t="n">
-        <v>-5.671799999999999</v>
+        <v>-0.5727</v>
       </c>
       <c r="P7" t="n">
-        <v>-6.3693</v>
+        <v>-0.965</v>
       </c>
       <c r="Q7" t="n">
-        <v>-35.5133</v>
+        <v>-2.123</v>
       </c>
       <c r="R7" t="n">
-        <v>29.144</v>
+        <v>1.158</v>
       </c>
       <c r="S7" t="n">
-        <v>-5.7903</v>
+        <v>0.5608</v>
       </c>
       <c r="T7" t="n">
-        <v>-4.0512</v>
+        <v>-0.11</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.7388</v>
+        <v>0.6708000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>8.257099999999999</v>
+        <v>-5.24</v>
       </c>
       <c r="W7" t="n">
-        <v>12.2697</v>
+        <v>-0.3704</v>
       </c>
       <c r="X7" t="n">
-        <v>-4.012600000000001</v>
+        <v>-4.8696</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.0642</v>
+        <v>-3.857</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5472</v>
+        <v>-2.6879</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.517</v>
+        <v>-1.169</v>
       </c>
       <c r="G8" t="n">
         <v>-1.8826</v>
@@ -1078,13 +1078,13 @@
         <v>2.316</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4456</v>
+        <v>-1.2384</v>
       </c>
       <c r="T8" t="n">
-        <v>0.234</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.6796</v>
+        <v>-1.3316</v>
       </c>
       <c r="V8" t="n">
         <v>-1.1221</v>
@@ -1111,13 +1111,13 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.385599999999999</v>
+        <v>-4.3969</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2813</v>
+        <v>-1.1217</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.1043</v>
+        <v>-3.2752</v>
       </c>
       <c r="G9" t="n">
         <v>-6.2292</v>
@@ -1156,13 +1156,13 @@
         <v>6.3693</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8307</v>
+        <v>0.1581</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7218</v>
+        <v>-0.5621</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1092</v>
+        <v>0.7202</v>
       </c>
       <c r="V9" t="n">
         <v>-1.7997</v>
@@ -1189,13 +1189,13 @@
         <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>-16.9471</v>
+        <v>-15.1431</v>
       </c>
       <c r="E10" t="n">
-        <v>-12.2106</v>
+        <v>-11.2091</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.737</v>
+        <v>-3.934</v>
       </c>
       <c r="G10" t="n">
         <v>-5.918699999999999</v>
@@ -1234,13 +1234,13 @@
         <v>5.211</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.7273</v>
+        <v>-1.9231</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.2487</v>
+        <v>-1.2473</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.4787</v>
+        <v>-0.6759000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-5.5643</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ALLAS MENESES</t>
+          <t>L. SANCHEZ TURRION</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>-21.3321</v>
+        <v>-21.1164</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.1126</v>
+        <v>-9.514799999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-12.2195</v>
+        <v>-11.6016</v>
       </c>
       <c r="G11" t="n">
-        <v>-39.9955</v>
+        <v>-21.1127</v>
       </c>
       <c r="H11" t="n">
-        <v>-27.708</v>
+        <v>-13.6431</v>
       </c>
       <c r="I11" t="n">
-        <v>-12.2874</v>
+        <v>-7.4696</v>
       </c>
       <c r="J11" t="n">
-        <v>6.516900000000001</v>
+        <v>-5.932</v>
       </c>
       <c r="K11" t="n">
-        <v>3.0336</v>
+        <v>-4.2134</v>
       </c>
       <c r="L11" t="n">
-        <v>3.4834</v>
+        <v>-1.7185</v>
       </c>
       <c r="M11" t="n">
-        <v>-46.5121</v>
+        <v>-15.1805</v>
       </c>
       <c r="N11" t="n">
-        <v>-30.7416</v>
+        <v>-9.429500000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-15.7706</v>
+        <v>-5.750999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-18.7217</v>
+        <v>5.5971</v>
       </c>
       <c r="Q11" t="n">
-        <v>-58.2882</v>
+        <v>-6.9481</v>
       </c>
       <c r="R11" t="n">
-        <v>39.5665</v>
+        <v>12.5452</v>
       </c>
       <c r="S11" t="n">
-        <v>17.8221</v>
+        <v>1.6398</v>
       </c>
       <c r="T11" t="n">
-        <v>8.455</v>
+        <v>1.9361</v>
       </c>
       <c r="U11" t="n">
-        <v>9.3674</v>
+        <v>-0.2964</v>
       </c>
       <c r="V11" t="n">
-        <v>19.5631</v>
+        <v>-7.2411</v>
       </c>
       <c r="W11" t="n">
-        <v>34.2044</v>
+        <v>1.4293</v>
       </c>
       <c r="X11" t="n">
-        <v>-14.6416</v>
+        <v>-8.670400000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. SANCHEZ TURRION</t>
+          <t>R. GONZALEZ RUIZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>-21.9857</v>
+        <v>-25.2558</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.3147</v>
+        <v>-14.1275</v>
       </c>
       <c r="F12" t="n">
-        <v>-12.6712</v>
+        <v>-11.1283</v>
       </c>
       <c r="G12" t="n">
-        <v>-21.1127</v>
+        <v>-18.938</v>
       </c>
       <c r="H12" t="n">
-        <v>-13.6431</v>
+        <v>-8.2441</v>
       </c>
       <c r="I12" t="n">
-        <v>-7.4696</v>
+        <v>-10.6939</v>
       </c>
       <c r="J12" t="n">
-        <v>-5.932</v>
+        <v>-4.1177</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.2134</v>
+        <v>3.2286</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.7185</v>
+        <v>-7.3463</v>
       </c>
       <c r="M12" t="n">
-        <v>-15.1805</v>
+        <v>-14.8202</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.429500000000001</v>
+        <v>-11.4728</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.750999999999999</v>
+        <v>-3.347499999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>5.5971</v>
+        <v>6.1761</v>
       </c>
       <c r="Q12" t="n">
-        <v>-6.9481</v>
+        <v>-6.3691</v>
       </c>
       <c r="R12" t="n">
-        <v>12.5452</v>
+        <v>12.5453</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7707000000000003</v>
+        <v>-6.078</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1365</v>
+        <v>-3.9262</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.3659</v>
+        <v>-2.1518</v>
       </c>
       <c r="V12" t="n">
-        <v>-7.2411</v>
+        <v>-6.415900000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4293</v>
+        <v>0.2859</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.670400000000001</v>
+        <v>-6.701700000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. GONZALEZ RUIZ</t>
+          <t>M. HERRERO CRESPO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>-27.9662</v>
+        <v>-25.2932</v>
       </c>
       <c r="E13" t="n">
-        <v>-16.0084</v>
+        <v>-4.317500000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.9576</v>
+        <v>-20.9759</v>
       </c>
       <c r="G13" t="n">
-        <v>-18.938</v>
+        <v>-3.993500000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-8.2441</v>
+        <v>9.8954</v>
       </c>
       <c r="I13" t="n">
-        <v>-10.6939</v>
+        <v>-13.8891</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.1177</v>
+        <v>57.0535</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2286</v>
+        <v>44.6446</v>
       </c>
       <c r="L13" t="n">
-        <v>-7.3463</v>
+        <v>12.4087</v>
       </c>
       <c r="M13" t="n">
-        <v>-14.8202</v>
+        <v>-61.0468</v>
       </c>
       <c r="N13" t="n">
-        <v>-11.4728</v>
+        <v>-34.7492</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.347499999999999</v>
+        <v>-26.2979</v>
       </c>
       <c r="P13" t="n">
-        <v>6.1761</v>
+        <v>-35.3204</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.3691</v>
+        <v>-88.3977</v>
       </c>
       <c r="R13" t="n">
-        <v>12.5453</v>
+        <v>53.0773</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.7883</v>
+        <v>-1.3204</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.8072</v>
+        <v>-7.4207</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.9812</v>
+        <v>6.1005</v>
       </c>
       <c r="V13" t="n">
-        <v>-6.415900000000001</v>
+        <v>15.3412</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2859</v>
+        <v>34.4479</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.701700000000001</v>
+        <v>-19.1068</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. ALLAS MENESES</t>
+          <t>S. MARTINEZ ORTIZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>-29.1558</v>
+        <v>-28.2022</v>
       </c>
       <c r="E14" t="n">
-        <v>-16.3094</v>
+        <v>-8.569900000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-12.8462</v>
+        <v>-19.632</v>
       </c>
       <c r="G14" t="n">
-        <v>-24.3361</v>
+        <v>-36.4924</v>
       </c>
       <c r="H14" t="n">
-        <v>-14.7084</v>
+        <v>-24.7431</v>
       </c>
       <c r="I14" t="n">
-        <v>-9.6282</v>
+        <v>-11.749</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.1696</v>
+        <v>11.9769</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.1853</v>
+        <v>8.1631</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01579999999999994</v>
+        <v>3.8142</v>
       </c>
       <c r="M14" t="n">
-        <v>-22.1662</v>
+        <v>-48.4693</v>
       </c>
       <c r="N14" t="n">
-        <v>-12.5226</v>
+        <v>-32.9059</v>
       </c>
       <c r="O14" t="n">
-        <v>-9.643699999999999</v>
+        <v>-15.5635</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3861999999999998</v>
+        <v>3.0883</v>
       </c>
       <c r="Q14" t="n">
-        <v>-17.1774</v>
+        <v>-44.7777</v>
       </c>
       <c r="R14" t="n">
-        <v>16.7914</v>
+        <v>47.8662</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9417999999999996</v>
+        <v>-4.1532</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.889</v>
+        <v>-7.114599999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.05249999999999994</v>
+        <v>2.9615</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.4915</v>
+        <v>9.355599999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>3.9277</v>
+        <v>31.3454</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.4192</v>
+        <v>-21.9902</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. BLANCO DE LA CRUZ</t>
+          <t>D. ALLAS MENESES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>-35.802</v>
+        <v>-28.8097</v>
       </c>
       <c r="E15" t="n">
-        <v>-16.7246</v>
+        <v>-17.2729</v>
       </c>
       <c r="F15" t="n">
-        <v>-19.0776</v>
+        <v>-11.5364</v>
       </c>
       <c r="G15" t="n">
-        <v>-19.1842</v>
+        <v>-24.3361</v>
       </c>
       <c r="H15" t="n">
-        <v>-10.2074</v>
+        <v>-14.7084</v>
       </c>
       <c r="I15" t="n">
-        <v>-8.976900000000001</v>
+        <v>-9.6282</v>
       </c>
       <c r="J15" t="n">
-        <v>1.817</v>
+        <v>-2.1696</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0539</v>
+        <v>-2.1853</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.2369000000000001</v>
+        <v>0.01579999999999994</v>
       </c>
       <c r="M15" t="n">
-        <v>-21.001</v>
+        <v>-22.1662</v>
       </c>
       <c r="N15" t="n">
-        <v>-12.2611</v>
+        <v>-12.5226</v>
       </c>
       <c r="O15" t="n">
-        <v>-8.74</v>
+        <v>-9.643699999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.895</v>
+        <v>-0.3861999999999998</v>
       </c>
       <c r="Q15" t="n">
-        <v>-17.7565</v>
+        <v>-17.1774</v>
       </c>
       <c r="R15" t="n">
-        <v>14.8614</v>
+        <v>16.7914</v>
       </c>
       <c r="S15" t="n">
-        <v>-5.1925</v>
+        <v>-0.5959999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9861</v>
+        <v>-1.8529</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.2067</v>
+        <v>1.2572</v>
       </c>
       <c r="V15" t="n">
-        <v>-8.5303</v>
+        <v>-3.4915</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2014</v>
+        <v>3.9277</v>
       </c>
       <c r="X15" t="n">
-        <v>-8.7317</v>
+        <v>-7.4192</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. HERRERO CRESPO</t>
+          <t>C. POLANCO MERINO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D16" t="n">
-        <v>-38.5737</v>
+        <v>-31.0018</v>
       </c>
       <c r="E16" t="n">
-        <v>-16.2904</v>
+        <v>-6.1629</v>
       </c>
       <c r="F16" t="n">
-        <v>-22.2833</v>
+        <v>-24.8386</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.993500000000001</v>
+        <v>-13.6518</v>
       </c>
       <c r="H16" t="n">
-        <v>9.8954</v>
+        <v>-7.9553</v>
       </c>
       <c r="I16" t="n">
-        <v>-13.8891</v>
+        <v>-5.6964</v>
       </c>
       <c r="J16" t="n">
-        <v>57.0535</v>
+        <v>10.6096</v>
       </c>
       <c r="K16" t="n">
-        <v>44.6446</v>
+        <v>6.063999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>12.4087</v>
+        <v>4.5457</v>
       </c>
       <c r="M16" t="n">
-        <v>-61.0468</v>
+        <v>-24.2608</v>
       </c>
       <c r="N16" t="n">
-        <v>-34.7492</v>
+        <v>-14.0188</v>
       </c>
       <c r="O16" t="n">
-        <v>-26.2979</v>
+        <v>-10.2421</v>
       </c>
       <c r="P16" t="n">
-        <v>-35.3204</v>
+        <v>0.3857</v>
       </c>
       <c r="Q16" t="n">
-        <v>-88.3977</v>
+        <v>-17.7566</v>
       </c>
       <c r="R16" t="n">
-        <v>53.0773</v>
+        <v>18.1424</v>
       </c>
       <c r="S16" t="n">
-        <v>-14.6008</v>
+        <v>-5.2551</v>
       </c>
       <c r="T16" t="n">
-        <v>-19.394</v>
+        <v>-2.4038</v>
       </c>
       <c r="U16" t="n">
-        <v>4.7934</v>
+        <v>-2.8511</v>
       </c>
       <c r="V16" t="n">
-        <v>15.3412</v>
+        <v>-12.4811</v>
       </c>
       <c r="W16" t="n">
-        <v>34.4479</v>
+        <v>3.3883</v>
       </c>
       <c r="X16" t="n">
-        <v>-19.1068</v>
+        <v>-15.8694</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. POLANCO MERINO</t>
+          <t>L. BLANCO DE LA CRUZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>-38.9595</v>
+        <v>-32.4641</v>
       </c>
       <c r="E17" t="n">
-        <v>-10.1876</v>
+        <v>-16.8652</v>
       </c>
       <c r="F17" t="n">
-        <v>-28.7721</v>
+        <v>-15.599</v>
       </c>
       <c r="G17" t="n">
-        <v>-13.6518</v>
+        <v>-19.1842</v>
       </c>
       <c r="H17" t="n">
-        <v>-7.9553</v>
+        <v>-10.2074</v>
       </c>
       <c r="I17" t="n">
-        <v>-5.6964</v>
+        <v>-8.976900000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>10.6096</v>
+        <v>1.817</v>
       </c>
       <c r="K17" t="n">
-        <v>6.063999999999999</v>
+        <v>2.0539</v>
       </c>
       <c r="L17" t="n">
-        <v>4.5457</v>
+        <v>-0.2369000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-24.2608</v>
+        <v>-21.001</v>
       </c>
       <c r="N17" t="n">
-        <v>-14.0188</v>
+        <v>-12.2611</v>
       </c>
       <c r="O17" t="n">
-        <v>-10.2421</v>
+        <v>-8.74</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3857</v>
+        <v>-2.895</v>
       </c>
       <c r="Q17" t="n">
-        <v>-17.7566</v>
+        <v>-17.7565</v>
       </c>
       <c r="R17" t="n">
-        <v>18.1424</v>
+        <v>14.8614</v>
       </c>
       <c r="S17" t="n">
-        <v>-13.2132</v>
+        <v>-1.8548</v>
       </c>
       <c r="T17" t="n">
-        <v>-6.4283</v>
+        <v>-1.1266</v>
       </c>
       <c r="U17" t="n">
-        <v>-6.7848</v>
+        <v>-0.728</v>
       </c>
       <c r="V17" t="n">
-        <v>-12.4811</v>
+        <v>-8.5303</v>
       </c>
       <c r="W17" t="n">
-        <v>3.3883</v>
+        <v>0.2014</v>
       </c>
       <c r="X17" t="n">
-        <v>-15.8694</v>
+        <v>-8.7317</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. MARTINEZ ORTIZ</t>
+          <t>A. ALLAS MENESES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>-47.8305</v>
+        <v>-34.1584</v>
       </c>
       <c r="E18" t="n">
-        <v>-22.2862</v>
+        <v>-17.9467</v>
       </c>
       <c r="F18" t="n">
-        <v>-25.5439</v>
+        <v>-16.2114</v>
       </c>
       <c r="G18" t="n">
-        <v>-36.4924</v>
+        <v>-39.9955</v>
       </c>
       <c r="H18" t="n">
-        <v>-24.7431</v>
+        <v>-27.708</v>
       </c>
       <c r="I18" t="n">
-        <v>-11.749</v>
+        <v>-12.2874</v>
       </c>
       <c r="J18" t="n">
-        <v>11.9769</v>
+        <v>6.516900000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>8.1631</v>
+        <v>3.0336</v>
       </c>
       <c r="L18" t="n">
-        <v>3.8142</v>
+        <v>3.4834</v>
       </c>
       <c r="M18" t="n">
-        <v>-48.4693</v>
+        <v>-46.5121</v>
       </c>
       <c r="N18" t="n">
-        <v>-32.9059</v>
+        <v>-30.7416</v>
       </c>
       <c r="O18" t="n">
-        <v>-15.5635</v>
+        <v>-15.7706</v>
       </c>
       <c r="P18" t="n">
-        <v>3.0883</v>
+        <v>-18.7217</v>
       </c>
       <c r="Q18" t="n">
-        <v>-44.7777</v>
+        <v>-58.2882</v>
       </c>
       <c r="R18" t="n">
-        <v>47.8662</v>
+        <v>39.5665</v>
       </c>
       <c r="S18" t="n">
-        <v>-23.7816</v>
+        <v>4.9961</v>
       </c>
       <c r="T18" t="n">
-        <v>-20.831</v>
+        <v>-0.3796000000000002</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.9506</v>
+        <v>5.3753</v>
       </c>
       <c r="V18" t="n">
-        <v>9.355599999999999</v>
+        <v>19.5631</v>
       </c>
       <c r="W18" t="n">
-        <v>31.3454</v>
+        <v>34.2044</v>
       </c>
       <c r="X18" t="n">
-        <v>-21.9902</v>
+        <v>-14.6416</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>-74.02549999999999</v>
+        <v>-65.07599999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-48.2197</v>
+        <v>-44.9151</v>
       </c>
       <c r="F19" t="n">
-        <v>-25.8058</v>
+        <v>-20.1609</v>
       </c>
       <c r="G19" t="n">
         <v>-48.9948</v>
@@ -1936,13 +1936,13 @@
         <v>37.2505</v>
       </c>
       <c r="S19" t="n">
-        <v>-12.9435</v>
+        <v>-3.9939</v>
       </c>
       <c r="T19" t="n">
-        <v>-6.3264</v>
+        <v>-3.0218</v>
       </c>
       <c r="U19" t="n">
-        <v>-6.616899999999999</v>
+        <v>-0.9722</v>
       </c>
       <c r="V19" t="n">
         <v>-6.104100000000001</v>
@@ -1969,13 +1969,13 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-275.529</v>
+        <v>-260.7635</v>
       </c>
       <c r="E20" t="n">
-        <v>-88.80090000000001</v>
+        <v>-86.71790000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-186.7291</v>
+        <v>-174.0448</v>
       </c>
       <c r="G20" t="n">
         <v>-262.7822</v>
@@ -2008,19 +2008,19 @@
         <v>-55.9729</v>
       </c>
       <c r="Q20" t="n">
-        <v>-414.9648999999999</v>
+        <v>-414.9649000000001</v>
       </c>
       <c r="R20" t="n">
         <v>358.9931</v>
       </c>
       <c r="S20" t="n">
-        <v>-14.945</v>
+        <v>-0.1783999999999994</v>
       </c>
       <c r="T20" t="n">
-        <v>-24.80679999999999</v>
+        <v>-22.7247</v>
       </c>
       <c r="U20" t="n">
-        <v>9.862600000000002</v>
+        <v>22.5468</v>
       </c>
       <c r="V20" t="n">
         <v>58.16919999999999</v>
